--- a/New_CenterOfRotation/Finite_COR/Data Files/C45_Data/Model 15 Y_Z Data.xlsx
+++ b/New_CenterOfRotation/Finite_COR/Data Files/C45_Data/Model 15 Y_Z Data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="3"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="4N"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="33">
   <si>
     <t>Node 25454</t>
   </si>
@@ -109,6 +109,9 @@
   </si>
   <si>
     <t>Bottom Back Left</t>
+  </si>
+  <si>
+    <t>Node:</t>
   </si>
   <si>
     <t>Orig Coords</t>
@@ -301,7 +304,7 @@
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="4" applyFill="1" quotePrefix="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -685,7 +688,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="30" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B2" s="1">
         <v>25454</v>
@@ -694,7 +697,7 @@
       <c r="D2" s="2"/>
       <c r="E2" s="3"/>
       <c r="F2" s="30" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G2" s="1">
         <v>31067</v>
@@ -703,7 +706,7 @@
       <c r="I2" s="2"/>
       <c r="J2" s="3"/>
       <c r="K2" s="30" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="L2" s="1">
         <v>29005</v>
@@ -712,7 +715,7 @@
       <c r="N2" s="2"/>
       <c r="O2" s="3"/>
       <c r="P2" s="30" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="Q2" s="1">
         <v>49903</v>
@@ -721,7 +724,7 @@
       <c r="S2" s="2"/>
       <c r="T2" s="3"/>
       <c r="U2" s="30" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="V2" s="1">
         <v>45615</v>
@@ -730,7 +733,7 @@
       <c r="X2" s="2"/>
       <c r="Y2" s="3"/>
       <c r="Z2" s="30" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AA2" s="1">
         <v>52027</v>
@@ -740,7 +743,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2">
         <v>-6.65384</v>
@@ -753,7 +756,7 @@
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3" s="2">
         <v>6.11839</v>
@@ -766,7 +769,7 @@
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L3" s="2">
         <v>0.185553</v>
@@ -779,7 +782,7 @@
       </c>
       <c r="O3" s="3"/>
       <c r="P3" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q3" s="2">
         <v>-0.732421</v>
@@ -792,7 +795,7 @@
       </c>
       <c r="T3" s="3"/>
       <c r="U3" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V3" s="2">
         <v>-8.27627</v>
@@ -805,7 +808,7 @@
       </c>
       <c r="Y3" s="3"/>
       <c r="Z3" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AA3" s="2">
         <v>7.72579</v>
@@ -822,7 +825,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>7</v>
@@ -835,7 +838,7 @@
         <v>6</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>7</v>
@@ -848,7 +851,7 @@
         <v>6</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M4" s="5" t="s">
         <v>7</v>
@@ -861,7 +864,7 @@
         <v>6</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="R4" s="5" t="s">
         <v>7</v>
@@ -874,7 +877,7 @@
         <v>6</v>
       </c>
       <c r="V4" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="W4" s="5" t="s">
         <v>7</v>
@@ -887,7 +890,7 @@
         <v>6</v>
       </c>
       <c r="AA4" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AB4" s="5" t="s">
         <v>7</v>
@@ -6503,7 +6506,7 @@
       <c r="AB3" s="2"/>
       <c r="AC3" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="22" t="s">
         <v>21</v>
       </c>

--- a/New_CenterOfRotation/Finite_COR/Data Files/C45_Data/Model 15 Y_Z Data.xlsx
+++ b/New_CenterOfRotation/Finite_COR/Data Files/C45_Data/Model 15 Y_Z Data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="2"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="4N"/>

--- a/New_CenterOfRotation/Finite_COR/Data Files/C45_Data/Model 15 Y_Z Data.xlsx
+++ b/New_CenterOfRotation/Finite_COR/Data Files/C45_Data/Model 15 Y_Z Data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="3"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="4N"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="32">
   <si>
     <t>Node 25454</t>
   </si>
@@ -90,9 +90,6 @@
     <t>X (U1)</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Top Right Front</t>
   </si>
   <si>
@@ -125,7 +122,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -142,6 +139,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -215,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -238,16 +241,19 @@
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -259,7 +265,10 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
@@ -268,44 +277,41 @@
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" quotePrefix="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="3" applyFill="1" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -612,75 +618,75 @@
   <dimension ref="A1:AC29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="27" max="27" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="28" max="28" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="29" max="29" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="26" max="26" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="27" max="27" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="28" max="28" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="29" max="29" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="29"/>
       <c r="D1" s="29"/>
       <c r="E1" s="10"/>
       <c r="F1" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G1" s="29"/>
       <c r="H1" s="29"/>
       <c r="I1" s="29"/>
       <c r="J1" s="10"/>
       <c r="K1" s="28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L1" s="29"/>
       <c r="M1" s="29"/>
       <c r="N1" s="29"/>
       <c r="O1" s="10"/>
       <c r="P1" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q1" s="29"/>
       <c r="R1" s="29"/>
       <c r="S1" s="29"/>
       <c r="T1" s="10"/>
       <c r="U1" s="28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V1" s="29"/>
       <c r="W1" s="29"/>
       <c r="X1" s="29"/>
       <c r="Y1" s="10"/>
       <c r="Z1" s="28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA1" s="29"/>
       <c r="AB1" s="29"/>
@@ -688,7 +694,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B2" s="1">
         <v>25454</v>
@@ -697,7 +703,7 @@
       <c r="D2" s="2"/>
       <c r="E2" s="3"/>
       <c r="F2" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G2" s="1">
         <v>31067</v>
@@ -706,7 +712,7 @@
       <c r="I2" s="2"/>
       <c r="J2" s="3"/>
       <c r="K2" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L2" s="1">
         <v>29005</v>
@@ -715,7 +721,7 @@
       <c r="N2" s="2"/>
       <c r="O2" s="3"/>
       <c r="P2" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q2" s="1">
         <v>49903</v>
@@ -724,7 +730,7 @@
       <c r="S2" s="2"/>
       <c r="T2" s="3"/>
       <c r="U2" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V2" s="1">
         <v>45615</v>
@@ -733,7 +739,7 @@
       <c r="X2" s="2"/>
       <c r="Y2" s="3"/>
       <c r="Z2" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA2" s="1">
         <v>52027</v>
@@ -743,7 +749,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B3" s="2">
         <v>-6.65384</v>
@@ -756,7 +762,7 @@
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G3" s="2">
         <v>6.11839</v>
@@ -769,7 +775,7 @@
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L3" s="2">
         <v>0.185553</v>
@@ -782,7 +788,7 @@
       </c>
       <c r="O3" s="3"/>
       <c r="P3" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q3" s="2">
         <v>-0.732421</v>
@@ -795,7 +801,7 @@
       </c>
       <c r="T3" s="3"/>
       <c r="U3" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V3" s="2">
         <v>-8.27627</v>
@@ -808,7 +814,7 @@
       </c>
       <c r="Y3" s="3"/>
       <c r="Z3" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AA3" s="2">
         <v>7.72579</v>
@@ -825,7 +831,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>7</v>
@@ -837,8 +843,8 @@
       <c r="F4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="9" t="s">
-        <v>32</v>
+      <c r="G4" s="31" t="s">
+        <v>31</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>7</v>
@@ -851,7 +857,7 @@
         <v>6</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M4" s="5" t="s">
         <v>7</v>
@@ -864,7 +870,7 @@
         <v>6</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R4" s="5" t="s">
         <v>7</v>
@@ -877,7 +883,7 @@
         <v>6</v>
       </c>
       <c r="V4" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="W4" s="5" t="s">
         <v>7</v>
@@ -890,7 +896,7 @@
         <v>6</v>
       </c>
       <c r="AA4" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AB4" s="5" t="s">
         <v>7</v>
@@ -2670,7 +2676,7 @@
       <c r="P29" s="8"/>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
-      <c r="S29" s="11"/>
+      <c r="S29" s="12"/>
       <c r="T29" s="10"/>
       <c r="U29" s="8"/>
       <c r="V29" s="9"/>
@@ -2695,29 +2701,29 @@
   <dimension ref="A1:W27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -4189,7 +4195,7 @@
       <c r="L27" s="10"/>
       <c r="M27" s="8"/>
       <c r="N27" s="9"/>
-      <c r="O27" s="11"/>
+      <c r="O27" s="12"/>
       <c r="P27" s="10"/>
       <c r="Q27" s="8"/>
       <c r="R27" s="9"/>
@@ -4220,35 +4226,35 @@
   <dimension ref="A1:AC30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="27" max="27" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="28" max="28" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="29" max="29" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="26" max="26" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="27" max="27" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="28" max="28" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="29" max="29" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -4289,179 +4295,167 @@
       <c r="AC1" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="3"/>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
       <c r="J2" s="3"/>
-      <c r="K2" s="16" t="s">
+      <c r="K2" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
       <c r="O2" s="3"/>
-      <c r="P2" s="18" t="s">
+      <c r="P2" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="17"/>
-      <c r="S2" s="17"/>
+      <c r="Q2" s="19"/>
+      <c r="R2" s="19"/>
+      <c r="S2" s="19"/>
       <c r="T2" s="3"/>
-      <c r="U2" s="16" t="s">
+      <c r="U2" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="V2" s="17"/>
-      <c r="W2" s="17"/>
-      <c r="X2" s="17"/>
+      <c r="V2" s="19"/>
+      <c r="W2" s="19"/>
+      <c r="X2" s="19"/>
       <c r="Y2" s="3"/>
-      <c r="Z2" s="16" t="s">
+      <c r="Z2" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="AA2" s="17"/>
-      <c r="AB2" s="17"/>
-      <c r="AC2" s="17"/>
+      <c r="AA2" s="19"/>
+      <c r="AB2" s="19"/>
+      <c r="AC2" s="19"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="26" t="s">
-        <v>23</v>
-      </c>
+      <c r="A3" s="21"/>
       <c r="B3" s="6">
         <v>25454</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
       <c r="E3" s="3"/>
-      <c r="F3" s="26" t="s">
-        <v>23</v>
-      </c>
+      <c r="F3" s="21"/>
       <c r="G3" s="6">
         <v>31067</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="3"/>
-      <c r="K3" s="26" t="s">
-        <v>23</v>
-      </c>
+      <c r="K3" s="21"/>
       <c r="L3" s="1">
         <v>29005</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="3"/>
-      <c r="P3" s="26" t="s">
-        <v>23</v>
-      </c>
+      <c r="P3" s="21"/>
       <c r="Q3" s="1">
         <v>45615</v>
       </c>
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
       <c r="T3" s="3"/>
-      <c r="U3" s="26" t="s">
-        <v>23</v>
-      </c>
+      <c r="U3" s="21"/>
       <c r="V3" s="1">
         <v>52027</v>
       </c>
       <c r="W3" s="2"/>
       <c r="X3" s="2"/>
       <c r="Y3" s="3"/>
-      <c r="Z3" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="AA3" s="21">
+      <c r="Z3" s="22"/>
+      <c r="AA3" s="23">
         <v>49903</v>
       </c>
       <c r="AB3" s="2"/>
       <c r="AC3" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="24" t="s">
         <v>21</v>
       </c>
       <c r="B4" s="7">
         <v>-6.65384</v>
       </c>
-      <c r="C4" s="23">
+      <c r="C4" s="25">
         <v>441.175</v>
       </c>
       <c r="D4" s="7">
         <v>-709.18</v>
       </c>
       <c r="E4" s="3"/>
-      <c r="F4" s="22" t="s">
+      <c r="F4" s="24" t="s">
         <v>21</v>
       </c>
       <c r="G4" s="7">
         <v>6.11839</v>
       </c>
-      <c r="H4" s="24">
+      <c r="H4" s="26">
         <v>439.835</v>
       </c>
       <c r="I4" s="7">
         <v>-709.539</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="K4" s="22" t="s">
+      <c r="K4" s="24" t="s">
         <v>21</v>
       </c>
       <c r="L4" s="2">
         <v>0.185553</v>
       </c>
-      <c r="M4" s="24">
+      <c r="M4" s="26">
         <v>446.547</v>
       </c>
       <c r="N4" s="2">
         <v>-707.74</v>
       </c>
       <c r="O4" s="3"/>
-      <c r="P4" s="22" t="s">
+      <c r="P4" s="24" t="s">
         <v>21</v>
       </c>
       <c r="Q4" s="2">
         <v>-8.27627</v>
       </c>
-      <c r="R4" s="23">
+      <c r="R4" s="25">
         <v>440.046</v>
       </c>
       <c r="S4" s="2">
         <v>-714.179</v>
       </c>
       <c r="T4" s="3"/>
-      <c r="U4" s="22" t="s">
+      <c r="U4" s="24" t="s">
         <v>21</v>
       </c>
       <c r="V4" s="2">
         <v>7.72579</v>
       </c>
-      <c r="W4" s="24">
+      <c r="W4" s="26">
         <v>440.224</v>
       </c>
       <c r="X4" s="2">
         <v>-714.622</v>
       </c>
       <c r="Y4" s="3"/>
-      <c r="Z4" s="22" t="s">
+      <c r="Z4" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="AA4" s="24">
+      <c r="AA4" s="26">
         <v>-0.0172085</v>
       </c>
-      <c r="AB4" s="23">
+      <c r="AB4" s="25">
         <v>445.307</v>
       </c>
-      <c r="AC4" s="24">
+      <c r="AC4" s="26">
         <v>-714.355</v>
       </c>
     </row>
@@ -4469,7 +4463,7 @@
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="27" t="s">
         <v>22</v>
       </c>
       <c r="C5" s="5" t="s">
@@ -4482,7 +4476,7 @@
       <c r="F5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="25" t="s">
+      <c r="G5" s="27" t="s">
         <v>22</v>
       </c>
       <c r="H5" s="5" t="s">
@@ -4495,7 +4489,7 @@
       <c r="K5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L5" s="25" t="s">
+      <c r="L5" s="27" t="s">
         <v>22</v>
       </c>
       <c r="M5" s="5" t="s">
@@ -4508,7 +4502,7 @@
       <c r="P5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Q5" s="25" t="s">
+      <c r="Q5" s="27" t="s">
         <v>22</v>
       </c>
       <c r="R5" s="5" t="s">
@@ -4521,7 +4515,7 @@
       <c r="U5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="V5" s="25" t="s">
+      <c r="V5" s="27" t="s">
         <v>22</v>
       </c>
       <c r="W5" s="5" t="s">
@@ -4534,7 +4528,7 @@
       <c r="Z5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AA5" s="25" t="s">
+      <c r="AA5" s="27" t="s">
         <v>22</v>
       </c>
       <c r="AB5" s="5" t="s">
@@ -6315,7 +6309,7 @@
       <c r="P30" s="8"/>
       <c r="Q30" s="9"/>
       <c r="R30" s="9"/>
-      <c r="S30" s="11"/>
+      <c r="S30" s="12"/>
       <c r="T30" s="10"/>
       <c r="U30" s="8"/>
       <c r="V30" s="9"/>
@@ -6340,35 +6334,35 @@
   <dimension ref="A1:AC30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="27" max="27" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="28" max="28" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="29" max="29" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="26" max="26" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="27" max="27" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="28" max="28" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="29" max="29" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -6409,50 +6403,50 @@
       <c r="AC1" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="3"/>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
       <c r="J2" s="3"/>
-      <c r="K2" s="16" t="s">
+      <c r="K2" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
       <c r="O2" s="3"/>
-      <c r="P2" s="18" t="s">
+      <c r="P2" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="17"/>
-      <c r="S2" s="17"/>
+      <c r="Q2" s="19"/>
+      <c r="R2" s="19"/>
+      <c r="S2" s="19"/>
       <c r="T2" s="3"/>
-      <c r="U2" s="16" t="s">
+      <c r="U2" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="V2" s="17"/>
-      <c r="W2" s="17"/>
-      <c r="X2" s="17"/>
+      <c r="V2" s="19"/>
+      <c r="W2" s="19"/>
+      <c r="X2" s="19"/>
       <c r="Y2" s="3"/>
-      <c r="Z2" s="16" t="s">
+      <c r="Z2" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="AA2" s="17"/>
-      <c r="AB2" s="17"/>
-      <c r="AC2" s="17"/>
+      <c r="AA2" s="19"/>
+      <c r="AB2" s="19"/>
+      <c r="AC2" s="19"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="21" t="s">
         <v>19</v>
       </c>
       <c r="B3" s="6">
@@ -6461,7 +6455,7 @@
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
       <c r="E3" s="3"/>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="21" t="s">
         <v>19</v>
       </c>
       <c r="G3" s="6">
@@ -6470,7 +6464,7 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="3"/>
-      <c r="K3" s="19" t="s">
+      <c r="K3" s="21" t="s">
         <v>19</v>
       </c>
       <c r="L3" s="1">
@@ -6479,7 +6473,7 @@
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="3"/>
-      <c r="P3" s="19" t="s">
+      <c r="P3" s="21" t="s">
         <v>19</v>
       </c>
       <c r="Q3" s="1">
@@ -6488,7 +6482,7 @@
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
       <c r="T3" s="3"/>
-      <c r="U3" s="19" t="s">
+      <c r="U3" s="21" t="s">
         <v>19</v>
       </c>
       <c r="V3" s="1">
@@ -6497,91 +6491,91 @@
       <c r="W3" s="2"/>
       <c r="X3" s="2"/>
       <c r="Y3" s="3"/>
-      <c r="Z3" s="20" t="s">
+      <c r="Z3" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="AA3" s="21">
+      <c r="AA3" s="23">
         <v>49903</v>
       </c>
       <c r="AB3" s="2"/>
       <c r="AC3" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="22" t="s">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+      <c r="A4" s="24" t="s">
         <v>21</v>
       </c>
       <c r="B4" s="7">
         <v>-6.65384</v>
       </c>
-      <c r="C4" s="23">
+      <c r="C4" s="25">
         <v>441.175</v>
       </c>
       <c r="D4" s="7">
         <v>-709.18</v>
       </c>
       <c r="E4" s="3"/>
-      <c r="F4" s="22" t="s">
+      <c r="F4" s="24" t="s">
         <v>21</v>
       </c>
       <c r="G4" s="7">
         <v>6.11839</v>
       </c>
-      <c r="H4" s="24">
+      <c r="H4" s="26">
         <v>439.835</v>
       </c>
       <c r="I4" s="7">
         <v>-709.539</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="K4" s="22" t="s">
+      <c r="K4" s="24" t="s">
         <v>21</v>
       </c>
       <c r="L4" s="2">
         <v>0.185553</v>
       </c>
-      <c r="M4" s="24">
+      <c r="M4" s="26">
         <v>446.547</v>
       </c>
       <c r="N4" s="2">
         <v>-707.74</v>
       </c>
       <c r="O4" s="3"/>
-      <c r="P4" s="22" t="s">
+      <c r="P4" s="24" t="s">
         <v>21</v>
       </c>
       <c r="Q4" s="2">
         <v>-8.27627</v>
       </c>
-      <c r="R4" s="23">
+      <c r="R4" s="25">
         <v>440.046</v>
       </c>
       <c r="S4" s="2">
         <v>-714.179</v>
       </c>
       <c r="T4" s="3"/>
-      <c r="U4" s="22" t="s">
+      <c r="U4" s="24" t="s">
         <v>21</v>
       </c>
       <c r="V4" s="2">
         <v>7.72579</v>
       </c>
-      <c r="W4" s="24">
+      <c r="W4" s="26">
         <v>440.224</v>
       </c>
       <c r="X4" s="2">
         <v>-714.622</v>
       </c>
       <c r="Y4" s="3"/>
-      <c r="Z4" s="22" t="s">
+      <c r="Z4" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="AA4" s="24">
+      <c r="AA4" s="26">
         <v>-0.0172085</v>
       </c>
-      <c r="AB4" s="23">
+      <c r="AB4" s="25">
         <v>445.307</v>
       </c>
-      <c r="AC4" s="24">
+      <c r="AC4" s="26">
         <v>-714.355</v>
       </c>
     </row>
@@ -6589,7 +6583,7 @@
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="27" t="s">
         <v>22</v>
       </c>
       <c r="C5" s="5" t="s">
@@ -6602,7 +6596,7 @@
       <c r="F5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="25" t="s">
+      <c r="G5" s="27" t="s">
         <v>22</v>
       </c>
       <c r="H5" s="5" t="s">
@@ -6615,7 +6609,7 @@
       <c r="K5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L5" s="25" t="s">
+      <c r="L5" s="27" t="s">
         <v>22</v>
       </c>
       <c r="M5" s="5" t="s">
@@ -6628,7 +6622,7 @@
       <c r="P5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Q5" s="25" t="s">
+      <c r="Q5" s="27" t="s">
         <v>22</v>
       </c>
       <c r="R5" s="5" t="s">
@@ -6641,7 +6635,7 @@
       <c r="U5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="V5" s="25" t="s">
+      <c r="V5" s="27" t="s">
         <v>22</v>
       </c>
       <c r="W5" s="5" t="s">
@@ -6654,7 +6648,7 @@
       <c r="Z5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AA5" s="25" t="s">
+      <c r="AA5" s="27" t="s">
         <v>22</v>
       </c>
       <c r="AB5" s="5" t="s">
@@ -8435,7 +8429,7 @@
       <c r="P30" s="8"/>
       <c r="Q30" s="9"/>
       <c r="R30" s="9"/>
-      <c r="S30" s="11"/>
+      <c r="S30" s="12"/>
       <c r="T30" s="10"/>
       <c r="U30" s="8"/>
       <c r="V30" s="9"/>
@@ -8460,29 +8454,29 @@
   <dimension ref="A1:W27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -9869,7 +9863,7 @@
       <c r="D24" s="10"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
-      <c r="G24" s="15">
+      <c r="G24" s="17">
         <v>-0.405779</v>
       </c>
       <c r="H24" s="10"/>
@@ -9954,7 +9948,7 @@
       <c r="L27" s="10"/>
       <c r="M27" s="8"/>
       <c r="N27" s="9"/>
-      <c r="O27" s="11"/>
+      <c r="O27" s="12"/>
       <c r="P27" s="10"/>
       <c r="Q27" s="8"/>
       <c r="R27" s="9"/>
@@ -9985,29 +9979,29 @@
   <dimension ref="A1:W27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -11415,7 +11409,7 @@
       <c r="W24" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="11" t="s">
         <v>9</v>
       </c>
       <c r="B25" s="9"/>
@@ -11481,7 +11475,7 @@
       <c r="L27" s="10"/>
       <c r="M27" s="8"/>
       <c r="N27" s="9"/>
-      <c r="O27" s="11"/>
+      <c r="O27" s="12"/>
       <c r="P27" s="10"/>
       <c r="Q27" s="8"/>
       <c r="R27" s="9"/>
